--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MUSEO HISTÓRICO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARRO</t>
+          <t>CORPORACION MUNICIPAL DE PENALOLEN PARA EL DESARROLO SOCIAL CORMUP</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18661,7 +18661,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Hospital San Jose - Casablanca</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -20430,12 +20430,12 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oficina de Seguimiento </t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
@@ -623,7 +623,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1192,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2285,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2728,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2854,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2980,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3045,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3171,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3236,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3301,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3366,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3492,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3618,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3683,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3809,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3874,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3939,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4065,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4191,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4256,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4321,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4386,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4451,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4577,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4642,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4707,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4772,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4837,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4902,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4967,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5032,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5097,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5162,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5288,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5353,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5418,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5483,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5609,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5674,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5739,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5926,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5991,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6056,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6121,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6369,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6434,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6499,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6625,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6751,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6816,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6942,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7129,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7194,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7259,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7385,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7450,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7637,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7702,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7828,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7893,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8080,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8145,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8271,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8336,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8462,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8588,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8653,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8718,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8905,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8970,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9035,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9100,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9287,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9535,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9722,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9848,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10157,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10344,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10470,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10657,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10722,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10970,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11035,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11161,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11226,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11413,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11478,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11543,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11608,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11673,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11738,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11864,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11929,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12055,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12120,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12185,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12250,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12315,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12380,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12445,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12510,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12697,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12762,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12888,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12953,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13018,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13144,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13209,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13274,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13339,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13404,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13469,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13656,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13843,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13969,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14034,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14465,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14530,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14656,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14721,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14847,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14973,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15099,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15164,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15290,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15355,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15420,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15485,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15611,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15676,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15741,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15928,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15993,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16058,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16123,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16188,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16253,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16318,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16444,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16570,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16635,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16822,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17009,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17074,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17139,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17204,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17330,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17395,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17521,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17586,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17651,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17716,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17842,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17907,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17972,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18037,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18224,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18289,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18354,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18419,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18484,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18549,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18614,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18679,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18744,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18809,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18874,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19000,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19065,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19130,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19195,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19260,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19325,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19390,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19455,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19581,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19646,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19711,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19837,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19902,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19967,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20154,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20219,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20284,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20349,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20414,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20540,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20605,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20670,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20735,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20800,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20865,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20991,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21056,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21121,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21186,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21373,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21438,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21503,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21568,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21633,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21698,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21885,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21950,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22015,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22080,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22145,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22210,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22275,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22340,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22649,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22714,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22779,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22844,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22909,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22974,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/jun-2026.xlsx
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -11645,7 +11645,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
